--- a/artfynd/A 63164-2025 artfynd.xlsx
+++ b/artfynd/A 63164-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>120664089</v>
       </c>
       <c r="B2" t="n">
-        <v>88024</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120663818</v>
+        <v>129536414</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>V Nyhammar, Dlr</t>
+          <t>Storslättberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493929</v>
+        <v>493949</v>
       </c>
       <c r="R3" t="n">
-        <v>6683486</v>
+        <v>6683695</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -863,31 +853,41 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Sofia Österdahl</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120664137</v>
+        <v>129537351</v>
       </c>
       <c r="B4" t="n">
-        <v>78601</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>V Nyhammar, Dlr</t>
+          <t>Storslättberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493959</v>
+        <v>493953</v>
       </c>
       <c r="R4" t="n">
-        <v>6683692</v>
+        <v>6683331</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -965,61 +965,76 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Sofia Österdahl</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129536414</v>
+        <v>120664137</v>
       </c>
       <c r="B5" t="n">
-        <v>89001</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storslättberget, Dlr</t>
+          <t>V Nyhammar, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493949</v>
+        <v>493959</v>
       </c>
       <c r="R5" t="n">
-        <v>6683695</v>
+        <v>6683692</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,12 +1061,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1062,87 +1077,64 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo, Sofia Österdahl</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132843038</v>
+        <v>129537353</v>
       </c>
       <c r="B6" t="n">
-        <v>57145</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storslättberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493933</v>
+        <v>493953</v>
       </c>
       <c r="R6" t="n">
-        <v>6683722</v>
+        <v>6683331</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1166,17 +1158,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ev. spelplats</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1187,19 +1174,241 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120663818</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>V Nyhammar, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>493929</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6683486</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Sofia Österdahl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132843038</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Storslättberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>493933</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6683722</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ev. spelplats</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Ulf Svensson</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Ulf Svensson</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
